--- a/spreadsheets/Week 7;.xlsx
+++ b/spreadsheets/Week 7;.xlsx
@@ -927,7 +927,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>17</v>

--- a/spreadsheets/Week 7;.xlsx
+++ b/spreadsheets/Week 7;.xlsx
@@ -927,7 +927,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>17</v>
